--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 лгрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3CE882-3F9C-4940-AB48-039102E41ABF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F5703E-5959-4565-9775-E022074E0BA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5298,7 +5298,8 @@
     <col min="22" max="31" width="6" customWidth="1"/>
     <col min="32" max="32" width="39.140625" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="50" width="3" customWidth="1"/>
+    <col min="34" max="34" width="7.7109375" customWidth="1"/>
+    <col min="35" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -5585,7 +5586,10 @@
       </c>
       <c r="AF4" s="12"/>
       <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
+      <c r="AH4" s="12">
+        <f>AH5*6</f>
+        <v>10004.792399999993</v>
+      </c>
       <c r="AI4" s="12"/>
       <c r="AJ4" s="12"/>
       <c r="AK4" s="12"/>
@@ -5703,7 +5707,10 @@
         <f>SUM(AG6:AG496)</f>
         <v>11464.83</v>
       </c>
-      <c r="AH5" s="12"/>
+      <c r="AH5" s="3">
+        <f>SUM(AH6:AH496)</f>
+        <v>1667.4653999999989</v>
+      </c>
       <c r="AI5" s="12"/>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="12"/>
@@ -5815,7 +5822,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="12"/>
+      <c r="AH6" s="12">
+        <f>P6*G6</f>
+        <v>0.76</v>
+      </c>
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
@@ -5930,7 +5940,10 @@
         <f t="shared" ref="AG7:AG70" si="8">G7*R7</f>
         <v>56</v>
       </c>
-      <c r="AH7" s="12"/>
+      <c r="AH7" s="12">
+        <f t="shared" ref="AH7:AH70" si="9">P7*G7</f>
+        <v>12</v>
+      </c>
       <c r="AI7" s="12"/>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="12"/>
@@ -6045,7 +6058,10 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="AH8" s="12"/>
+      <c r="AH8" s="12">
+        <f t="shared" si="9"/>
+        <v>7.0340000000000007</v>
+      </c>
       <c r="AI8" s="12"/>
       <c r="AJ8" s="12"/>
       <c r="AK8" s="12"/>
@@ -6157,7 +6173,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH9" s="12"/>
+      <c r="AH9" s="12">
+        <f t="shared" si="9"/>
+        <v>2.0499999999999998</v>
+      </c>
       <c r="AI9" s="12"/>
       <c r="AJ9" s="12"/>
       <c r="AK9" s="12"/>
@@ -6272,7 +6291,10 @@
         <f t="shared" si="8"/>
         <v>969</v>
       </c>
-      <c r="AH10" s="12"/>
+      <c r="AH10" s="12">
+        <f t="shared" si="9"/>
+        <v>142.6754</v>
+      </c>
       <c r="AI10" s="12"/>
       <c r="AJ10" s="12"/>
       <c r="AK10" s="12"/>
@@ -6387,7 +6409,10 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AH11" s="12"/>
+      <c r="AH11" s="12">
+        <f t="shared" si="9"/>
+        <v>6.5245999999999995</v>
+      </c>
       <c r="AI11" s="12"/>
       <c r="AJ11" s="12"/>
       <c r="AK11" s="12"/>
@@ -6500,7 +6525,10 @@
         <f t="shared" si="8"/>
         <v>214</v>
       </c>
-      <c r="AH12" s="12"/>
+      <c r="AH12" s="12">
+        <f t="shared" si="9"/>
+        <v>40.245199999999997</v>
+      </c>
       <c r="AI12" s="12"/>
       <c r="AJ12" s="12"/>
       <c r="AK12" s="12"/>
@@ -6615,7 +6643,10 @@
         <f t="shared" si="8"/>
         <v>420</v>
       </c>
-      <c r="AH13" s="12"/>
+      <c r="AH13" s="12">
+        <f t="shared" si="9"/>
+        <v>55.126199999999997</v>
+      </c>
       <c r="AI13" s="12"/>
       <c r="AJ13" s="12"/>
       <c r="AK13" s="12"/>
@@ -6729,7 +6760,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="12"/>
+      <c r="AH14" s="12">
+        <f t="shared" si="9"/>
+        <v>3.75</v>
+      </c>
       <c r="AI14" s="12"/>
       <c r="AJ14" s="12"/>
       <c r="AK14" s="12"/>
@@ -6839,7 +6873,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="12"/>
+      <c r="AH15" s="12">
+        <f t="shared" si="9"/>
+        <v>11.143600000000001</v>
+      </c>
       <c r="AI15" s="12"/>
       <c r="AJ15" s="12"/>
       <c r="AK15" s="12"/>
@@ -6952,7 +6989,10 @@
         <f t="shared" si="8"/>
         <v>8.5</v>
       </c>
-      <c r="AH16" s="12"/>
+      <c r="AH16" s="12">
+        <f t="shared" si="9"/>
+        <v>7.5</v>
+      </c>
       <c r="AI16" s="12"/>
       <c r="AJ16" s="12"/>
       <c r="AK16" s="12"/>
@@ -7065,7 +7105,10 @@
         <f t="shared" si="8"/>
         <v>67.600000000000009</v>
       </c>
-      <c r="AH17" s="12"/>
+      <c r="AH17" s="12">
+        <f t="shared" si="9"/>
+        <v>8.4</v>
+      </c>
       <c r="AI17" s="12"/>
       <c r="AJ17" s="12"/>
       <c r="AK17" s="12"/>
@@ -7183,7 +7226,10 @@
         <f t="shared" si="8"/>
         <v>400</v>
       </c>
-      <c r="AH18" s="12"/>
+      <c r="AH18" s="12">
+        <f t="shared" si="9"/>
+        <v>60.1004</v>
+      </c>
       <c r="AI18" s="12"/>
       <c r="AJ18" s="12"/>
       <c r="AK18" s="12"/>
@@ -7295,7 +7341,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="12"/>
+      <c r="AH19" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI19" s="12"/>
       <c r="AJ19" s="12"/>
       <c r="AK19" s="12"/>
@@ -7413,7 +7462,10 @@
         <f t="shared" si="8"/>
         <v>64</v>
       </c>
-      <c r="AH20" s="12"/>
+      <c r="AH20" s="12">
+        <f t="shared" si="9"/>
+        <v>6.48</v>
+      </c>
       <c r="AI20" s="12"/>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="12"/>
@@ -7475,7 +7527,7 @@
         <v>56.331399999999995</v>
       </c>
       <c r="Q21" s="4">
-        <f t="shared" ref="Q21:Q31" si="9">15*P21-O21-F21</f>
+        <f t="shared" ref="Q21:Q31" si="10">15*P21-O21-F21</f>
         <v>262.32199999999989</v>
       </c>
       <c r="R21" s="4">
@@ -7526,7 +7578,10 @@
         <f t="shared" si="8"/>
         <v>262</v>
       </c>
-      <c r="AH21" s="12"/>
+      <c r="AH21" s="12">
+        <f t="shared" si="9"/>
+        <v>56.331399999999995</v>
+      </c>
       <c r="AI21" s="12"/>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="12"/>
@@ -7590,7 +7645,7 @@
         <v>27.4</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="R22" s="4">
@@ -7646,7 +7701,10 @@
         <f t="shared" si="8"/>
         <v>44</v>
       </c>
-      <c r="AH22" s="12"/>
+      <c r="AH22" s="12">
+        <f t="shared" si="9"/>
+        <v>6.0279999999999996</v>
+      </c>
       <c r="AI22" s="12"/>
       <c r="AJ22" s="12"/>
       <c r="AK22" s="12"/>
@@ -7710,7 +7768,7 @@
         <v>8.9047999999999998</v>
       </c>
       <c r="Q23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>60.663000000000004</v>
       </c>
       <c r="R23" s="4">
@@ -7763,7 +7821,10 @@
         <f t="shared" si="8"/>
         <v>61</v>
       </c>
-      <c r="AH23" s="12"/>
+      <c r="AH23" s="12">
+        <f t="shared" si="9"/>
+        <v>8.9047999999999998</v>
+      </c>
       <c r="AI23" s="12"/>
       <c r="AJ23" s="12"/>
       <c r="AK23" s="12"/>
@@ -7876,7 +7937,10 @@
         <f t="shared" si="8"/>
         <v>325</v>
       </c>
-      <c r="AH24" s="12"/>
+      <c r="AH24" s="12">
+        <f t="shared" si="9"/>
+        <v>42.6342</v>
+      </c>
       <c r="AI24" s="12"/>
       <c r="AJ24" s="12"/>
       <c r="AK24" s="12"/>
@@ -7940,7 +8004,7 @@
         <v>50.6</v>
       </c>
       <c r="Q25" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>246</v>
       </c>
       <c r="R25" s="4">
@@ -7994,7 +8058,10 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="AH25" s="12"/>
+      <c r="AH25" s="12">
+        <f t="shared" si="9"/>
+        <v>4.5540000000000003</v>
+      </c>
       <c r="AI25" s="12"/>
       <c r="AJ25" s="12"/>
       <c r="AK25" s="12"/>
@@ -8058,7 +8125,7 @@
         <v>29.8</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>165</v>
       </c>
       <c r="R26" s="4">
@@ -8109,7 +8176,10 @@
         <f t="shared" si="8"/>
         <v>14.85</v>
       </c>
-      <c r="AH26" s="12"/>
+      <c r="AH26" s="12">
+        <f t="shared" si="9"/>
+        <v>2.6819999999999999</v>
+      </c>
       <c r="AI26" s="12"/>
       <c r="AJ26" s="12"/>
       <c r="AK26" s="12"/>
@@ -8173,7 +8243,7 @@
         <v>23.4</v>
       </c>
       <c r="Q27" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="R27" s="4">
@@ -8227,7 +8297,10 @@
         <f t="shared" si="8"/>
         <v>4.5</v>
       </c>
-      <c r="AH27" s="12"/>
+      <c r="AH27" s="12">
+        <f t="shared" si="9"/>
+        <v>3.51</v>
+      </c>
       <c r="AI27" s="12"/>
       <c r="AJ27" s="12"/>
       <c r="AK27" s="12"/>
@@ -8342,7 +8415,10 @@
         <f t="shared" si="8"/>
         <v>620</v>
       </c>
-      <c r="AH28" s="12"/>
+      <c r="AH28" s="12">
+        <f t="shared" si="9"/>
+        <v>74.251599999999996</v>
+      </c>
       <c r="AI28" s="12"/>
       <c r="AJ28" s="12"/>
       <c r="AK28" s="12"/>
@@ -8406,7 +8482,7 @@
         <v>41.8</v>
       </c>
       <c r="Q29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>119</v>
       </c>
       <c r="R29" s="4">
@@ -8462,7 +8538,10 @@
         <f t="shared" si="8"/>
         <v>60</v>
       </c>
-      <c r="AH29" s="12"/>
+      <c r="AH29" s="12">
+        <f t="shared" si="9"/>
+        <v>16.72</v>
+      </c>
       <c r="AI29" s="12"/>
       <c r="AJ29" s="12"/>
       <c r="AK29" s="12"/>
@@ -8526,7 +8605,7 @@
         <v>55.8</v>
       </c>
       <c r="Q30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>306</v>
       </c>
       <c r="R30" s="4">
@@ -8577,7 +8656,10 @@
         <f t="shared" si="8"/>
         <v>122.4</v>
       </c>
-      <c r="AH30" s="12"/>
+      <c r="AH30" s="12">
+        <f t="shared" si="9"/>
+        <v>22.32</v>
+      </c>
       <c r="AI30" s="12"/>
       <c r="AJ30" s="12"/>
       <c r="AK30" s="12"/>
@@ -8641,7 +8723,7 @@
         <v>36</v>
       </c>
       <c r="Q31" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="R31" s="4">
@@ -8695,7 +8777,10 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
-      <c r="AH31" s="12"/>
+      <c r="AH31" s="12">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
       <c r="AI31" s="12"/>
       <c r="AJ31" s="12"/>
       <c r="AK31" s="12"/>
@@ -8811,7 +8896,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="12"/>
+      <c r="AH32" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI32" s="12"/>
       <c r="AJ32" s="12"/>
       <c r="AK32" s="12"/>
@@ -8925,7 +9013,10 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AH33" s="12"/>
+      <c r="AH33" s="12">
+        <f t="shared" si="9"/>
+        <v>13.143799999999999</v>
+      </c>
       <c r="AI33" s="12"/>
       <c r="AJ33" s="12"/>
       <c r="AK33" s="12"/>
@@ -9040,7 +9131,10 @@
         <f t="shared" si="8"/>
         <v>189</v>
       </c>
-      <c r="AH34" s="12"/>
+      <c r="AH34" s="12">
+        <f t="shared" si="9"/>
+        <v>28.796800000000001</v>
+      </c>
       <c r="AI34" s="12"/>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="12"/>
@@ -9102,7 +9196,7 @@
         <v>25.0062</v>
       </c>
       <c r="Q35" s="4">
-        <f t="shared" ref="Q35" si="10">15*P35-O35-F35</f>
+        <f t="shared" ref="Q35" si="11">15*P35-O35-F35</f>
         <v>137.95900000000003</v>
       </c>
       <c r="R35" s="4">
@@ -9153,7 +9247,10 @@
         <f t="shared" si="8"/>
         <v>138</v>
       </c>
-      <c r="AH35" s="12"/>
+      <c r="AH35" s="12">
+        <f t="shared" si="9"/>
+        <v>25.0062</v>
+      </c>
       <c r="AI35" s="12"/>
       <c r="AJ35" s="12"/>
       <c r="AK35" s="12"/>
@@ -9263,7 +9360,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="12"/>
+      <c r="AH36" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI36" s="12"/>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="12"/>
@@ -9327,7 +9427,7 @@
         <v>24.169599999999999</v>
       </c>
       <c r="Q37" s="4">
-        <f t="shared" ref="Q37:Q79" si="11">15*P37-O37-F37</f>
+        <f t="shared" ref="Q37:Q79" si="12">15*P37-O37-F37</f>
         <v>59.085999999999956</v>
       </c>
       <c r="R37" s="4">
@@ -9378,7 +9478,10 @@
         <f t="shared" si="8"/>
         <v>59</v>
       </c>
-      <c r="AH37" s="12"/>
+      <c r="AH37" s="12">
+        <f t="shared" si="9"/>
+        <v>24.169599999999999</v>
+      </c>
       <c r="AI37" s="12"/>
       <c r="AJ37" s="12"/>
       <c r="AK37" s="12"/>
@@ -9429,7 +9532,7 @@
         <v>282</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-19</v>
       </c>
       <c r="M38" s="12"/>
@@ -9438,7 +9541,7 @@
         <v>41</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>52.6</v>
       </c>
       <c r="Q38" s="4">
@@ -9455,7 +9558,7 @@
         <v>13.992395437262356</v>
       </c>
       <c r="U38" s="12">
-        <f t="shared" ref="U38:U69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="15">(F38+O38)/P38</f>
         <v>5.5323193916349807</v>
       </c>
       <c r="V38" s="12">
@@ -9493,7 +9596,10 @@
         <f t="shared" si="8"/>
         <v>133.5</v>
       </c>
-      <c r="AH38" s="12"/>
+      <c r="AH38" s="12">
+        <f t="shared" si="9"/>
+        <v>15.78</v>
+      </c>
       <c r="AI38" s="12"/>
       <c r="AJ38" s="12"/>
       <c r="AK38" s="12"/>
@@ -9544,7 +9650,7 @@
         <v>185.9</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6689999999999827</v>
       </c>
       <c r="M39" s="12"/>
@@ -9553,11 +9659,11 @@
         <v>0</v>
       </c>
       <c r="P39" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>37.513799999999996</v>
       </c>
       <c r="Q39" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>210.42399999999998</v>
       </c>
       <c r="R39" s="4">
@@ -9570,7 +9676,7 @@
         <v>14.988697492656037</v>
       </c>
       <c r="U39" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.3907575345606169</v>
       </c>
       <c r="V39" s="12">
@@ -9608,7 +9714,10 @@
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="AH39" s="12"/>
+      <c r="AH39" s="12">
+        <f t="shared" si="9"/>
+        <v>37.513799999999996</v>
+      </c>
       <c r="AI39" s="12"/>
       <c r="AJ39" s="12"/>
       <c r="AK39" s="12"/>
@@ -9659,7 +9768,7 @@
         <v>417.5</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>25.259000000000015</v>
       </c>
       <c r="M40" s="12"/>
@@ -9668,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>88.5518</v>
       </c>
       <c r="Q40" s="4">
@@ -9685,7 +9794,7 @@
         <v>11.004112846943823</v>
       </c>
       <c r="U40" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.1104280206613533</v>
       </c>
       <c r="V40" s="12">
@@ -9723,7 +9832,10 @@
         <f t="shared" si="8"/>
         <v>699</v>
       </c>
-      <c r="AH40" s="12"/>
+      <c r="AH40" s="12">
+        <f t="shared" si="9"/>
+        <v>88.5518</v>
+      </c>
       <c r="AI40" s="12"/>
       <c r="AJ40" s="12"/>
       <c r="AK40" s="12"/>
@@ -9774,7 +9886,7 @@
         <v>412</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-30</v>
       </c>
       <c r="M41" s="12"/>
@@ -9783,11 +9895,11 @@
         <v>149</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>76.400000000000006</v>
       </c>
       <c r="Q41" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>636</v>
       </c>
       <c r="R41" s="4">
@@ -9800,7 +9912,7 @@
         <v>14.999999999999998</v>
       </c>
       <c r="U41" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.6753926701570672</v>
       </c>
       <c r="V41" s="12">
@@ -9838,7 +9950,10 @@
         <f t="shared" si="8"/>
         <v>222.6</v>
       </c>
-      <c r="AH41" s="12"/>
+      <c r="AH41" s="12">
+        <f t="shared" si="9"/>
+        <v>26.740000000000002</v>
+      </c>
       <c r="AI41" s="12"/>
       <c r="AJ41" s="12"/>
       <c r="AK41" s="12"/>
@@ -9889,7 +10004,7 @@
         <v>293</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-81</v>
       </c>
       <c r="M42" s="12"/>
@@ -9898,7 +10013,7 @@
         <v>85</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42.4</v>
       </c>
       <c r="Q42" s="4">
@@ -9915,7 +10030,7 @@
         <v>14.009433962264151</v>
       </c>
       <c r="U42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.7783018867924527</v>
       </c>
       <c r="V42" s="12">
@@ -9953,7 +10068,10 @@
         <f t="shared" si="8"/>
         <v>143.09</v>
       </c>
-      <c r="AH42" s="12"/>
+      <c r="AH42" s="12">
+        <f t="shared" si="9"/>
+        <v>17.383999999999997</v>
+      </c>
       <c r="AI42" s="12"/>
       <c r="AJ42" s="12"/>
       <c r="AK42" s="12"/>
@@ -10004,7 +10122,7 @@
         <v>130</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-8</v>
       </c>
       <c r="M43" s="12"/>
@@ -10013,11 +10131,11 @@
         <v>73</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.4</v>
       </c>
       <c r="Q43" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>125</v>
       </c>
       <c r="R43" s="4">
@@ -10030,7 +10148,7 @@
         <v>15</v>
       </c>
       <c r="U43" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.8770491803278695</v>
       </c>
       <c r="V43" s="12">
@@ -10068,7 +10186,10 @@
         <f t="shared" si="8"/>
         <v>51.25</v>
       </c>
-      <c r="AH43" s="12"/>
+      <c r="AH43" s="12">
+        <f t="shared" si="9"/>
+        <v>10.004</v>
+      </c>
       <c r="AI43" s="12"/>
       <c r="AJ43" s="12"/>
       <c r="AK43" s="12"/>
@@ -10119,7 +10240,7 @@
         <v>316</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M44" s="12"/>
@@ -10128,7 +10249,7 @@
         <v>236</v>
       </c>
       <c r="P44" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>61.2</v>
       </c>
       <c r="Q44" s="4">
@@ -10145,7 +10266,7 @@
         <v>13.006535947712418</v>
       </c>
       <c r="U44" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.3431372549019605</v>
       </c>
       <c r="V44" s="12">
@@ -10185,7 +10306,10 @@
         <f t="shared" si="8"/>
         <v>168.84</v>
       </c>
-      <c r="AH44" s="12"/>
+      <c r="AH44" s="12">
+        <f t="shared" si="9"/>
+        <v>22.032</v>
+      </c>
       <c r="AI44" s="12"/>
       <c r="AJ44" s="12"/>
       <c r="AK44" s="12"/>
@@ -10236,7 +10360,7 @@
         <v>97</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-21</v>
       </c>
       <c r="M45" s="12"/>
@@ -10245,7 +10369,7 @@
         <v>9</v>
       </c>
       <c r="P45" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.2</v>
       </c>
       <c r="Q45" s="4">
@@ -10253,7 +10377,7 @@
         <v>124.79999999999998</v>
       </c>
       <c r="R45" s="4">
-        <f t="shared" ref="R45:R50" si="15">S45</f>
+        <f t="shared" ref="R45:R50" si="16">S45</f>
         <v>170</v>
       </c>
       <c r="S45" s="25">
@@ -10265,7 +10389,7 @@
         <v>11.973684210526317</v>
       </c>
       <c r="U45" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="V45" s="12">
@@ -10303,7 +10427,10 @@
         <f t="shared" si="8"/>
         <v>56.1</v>
       </c>
-      <c r="AH45" s="12"/>
+      <c r="AH45" s="12">
+        <f t="shared" si="9"/>
+        <v>5.016</v>
+      </c>
       <c r="AI45" s="12"/>
       <c r="AJ45" s="12"/>
       <c r="AK45" s="12"/>
@@ -10352,7 +10479,7 @@
         <v>68</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-17</v>
       </c>
       <c r="M46" s="12"/>
@@ -10361,15 +10488,15 @@
         <v>0</v>
       </c>
       <c r="P46" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.199999999999999</v>
       </c>
       <c r="Q46" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>74</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="S46" s="25">
@@ -10381,7 +10508,7 @@
         <v>17.549019607843139</v>
       </c>
       <c r="U46" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.7450980392156872</v>
       </c>
       <c r="V46" s="12">
@@ -10419,7 +10546,10 @@
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="AH46" s="12"/>
+      <c r="AH46" s="12">
+        <f t="shared" si="9"/>
+        <v>4.08</v>
+      </c>
       <c r="AI46" s="12"/>
       <c r="AJ46" s="12"/>
       <c r="AK46" s="12"/>
@@ -10470,7 +10600,7 @@
         <v>40</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M47" s="12"/>
@@ -10479,15 +10609,15 @@
         <v>30</v>
       </c>
       <c r="P47" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>54</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>80</v>
       </c>
       <c r="S47" s="25">
@@ -10499,7 +10629,7 @@
         <v>18.25</v>
       </c>
       <c r="U47" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.25</v>
       </c>
       <c r="V47" s="12">
@@ -10537,7 +10667,10 @@
         <f t="shared" si="8"/>
         <v>26.400000000000002</v>
       </c>
-      <c r="AH47" s="12"/>
+      <c r="AH47" s="12">
+        <f t="shared" si="9"/>
+        <v>2.64</v>
+      </c>
       <c r="AI47" s="12"/>
       <c r="AJ47" s="12"/>
       <c r="AK47" s="12"/>
@@ -10588,7 +10721,7 @@
         <v>460.4</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29.010000000000048</v>
       </c>
       <c r="M48" s="12"/>
@@ -10597,7 +10730,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>97.882000000000005</v>
       </c>
       <c r="Q48" s="4">
@@ -10605,7 +10738,7 @@
         <v>744.75</v>
       </c>
       <c r="R48" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>900</v>
       </c>
       <c r="S48" s="25">
@@ -10617,7 +10750,7 @@
         <v>11.586093459471607</v>
       </c>
       <c r="U48" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.3913487668825728</v>
       </c>
       <c r="V48" s="12">
@@ -10655,7 +10788,10 @@
         <f t="shared" si="8"/>
         <v>900</v>
       </c>
-      <c r="AH48" s="12"/>
+      <c r="AH48" s="12">
+        <f t="shared" si="9"/>
+        <v>97.882000000000005</v>
+      </c>
       <c r="AI48" s="12"/>
       <c r="AJ48" s="12"/>
       <c r="AK48" s="12"/>
@@ -10704,7 +10840,7 @@
         <v>45</v>
       </c>
       <c r="L49" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-14</v>
       </c>
       <c r="M49" s="12"/>
@@ -10713,15 +10849,15 @@
         <v>0</v>
       </c>
       <c r="P49" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.2</v>
       </c>
       <c r="Q49" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>80</v>
       </c>
       <c r="S49" s="25">
@@ -10733,7 +10869,7 @@
         <v>20.967741935483872</v>
       </c>
       <c r="U49" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.064516129032258</v>
       </c>
       <c r="V49" s="12">
@@ -10771,7 +10907,10 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
-      <c r="AH49" s="12"/>
+      <c r="AH49" s="12">
+        <f t="shared" si="9"/>
+        <v>2.4800000000000004</v>
+      </c>
       <c r="AI49" s="12"/>
       <c r="AJ49" s="12"/>
       <c r="AK49" s="12"/>
@@ -10820,7 +10959,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="L50" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.33500000000000085</v>
       </c>
       <c r="M50" s="12"/>
@@ -10829,15 +10968,15 @@
         <v>0</v>
       </c>
       <c r="P50" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5529999999999999</v>
       </c>
       <c r="Q50" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19.821000000000005</v>
       </c>
       <c r="R50" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="S50" s="25">
@@ -10849,7 +10988,7 @@
         <v>17.864902898958626</v>
       </c>
       <c r="U50" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.4213340838727824</v>
       </c>
       <c r="V50" s="12">
@@ -10889,7 +11028,10 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="AH50" s="12"/>
+      <c r="AH50" s="12">
+        <f t="shared" si="9"/>
+        <v>3.5529999999999999</v>
+      </c>
       <c r="AI50" s="12"/>
       <c r="AJ50" s="12"/>
       <c r="AK50" s="12"/>
@@ -10938,7 +11080,7 @@
         <v>32.4</v>
       </c>
       <c r="L51" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.0719999999999992</v>
       </c>
       <c r="M51" s="12"/>
@@ -10947,11 +11089,11 @@
         <v>20</v>
       </c>
       <c r="P51" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.0655999999999999</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>48.544999999999995</v>
       </c>
       <c r="R51" s="4">
@@ -10964,7 +11106,7 @@
         <v>15.075013189132154</v>
       </c>
       <c r="U51" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9966697441308368</v>
       </c>
       <c r="V51" s="12">
@@ -11002,7 +11144,10 @@
         <f t="shared" si="8"/>
         <v>49</v>
       </c>
-      <c r="AH51" s="12"/>
+      <c r="AH51" s="12">
+        <f t="shared" si="9"/>
+        <v>6.0655999999999999</v>
+      </c>
       <c r="AI51" s="12"/>
       <c r="AJ51" s="12"/>
       <c r="AK51" s="12"/>
@@ -11047,7 +11192,7 @@
         <v>2.6</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3.1280000000000001</v>
       </c>
       <c r="M52" s="12"/>
@@ -11056,7 +11201,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.1056</v>
       </c>
       <c r="Q52" s="19">
@@ -11072,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V52" s="12">
@@ -11112,7 +11257,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="12"/>
+      <c r="AH52" s="12">
+        <f t="shared" si="9"/>
+        <v>-0.1056</v>
+      </c>
       <c r="AI52" s="12"/>
       <c r="AJ52" s="12"/>
       <c r="AK52" s="12"/>
@@ -11163,7 +11311,7 @@
         <v>57</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M53" s="12"/>
@@ -11172,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.4</v>
       </c>
       <c r="Q53" s="4">
@@ -11180,7 +11328,7 @@
         <v>71.2</v>
       </c>
       <c r="R53" s="4">
-        <f t="shared" ref="R53:R55" si="16">S53</f>
+        <f t="shared" ref="R53:R55" si="17">S53</f>
         <v>100</v>
       </c>
       <c r="S53" s="25">
@@ -11192,7 +11340,7 @@
         <v>16.063829787234042</v>
       </c>
       <c r="U53" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.4255319148936172</v>
       </c>
       <c r="V53" s="12">
@@ -11230,7 +11378,10 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="AH53" s="12"/>
+      <c r="AH53" s="12">
+        <f t="shared" si="9"/>
+        <v>2.35</v>
+      </c>
       <c r="AI53" s="12"/>
       <c r="AJ53" s="12"/>
       <c r="AK53" s="12"/>
@@ -11279,7 +11430,7 @@
         <v>41.1</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.6670000000000016</v>
       </c>
       <c r="M54" s="12"/>
@@ -11288,12 +11439,12 @@
         <v>0</v>
       </c>
       <c r="P54" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.8865999999999996</v>
       </c>
       <c r="Q54" s="4"/>
       <c r="R54" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
       <c r="S54" s="25">
@@ -11305,7 +11456,7 @@
         <v>29.598052392666041</v>
       </c>
       <c r="U54" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.258184769102023</v>
       </c>
       <c r="V54" s="12">
@@ -11345,7 +11496,10 @@
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="AH54" s="12"/>
+      <c r="AH54" s="12">
+        <f t="shared" si="9"/>
+        <v>7.8865999999999996</v>
+      </c>
       <c r="AI54" s="12"/>
       <c r="AJ54" s="12"/>
       <c r="AK54" s="12"/>
@@ -11394,7 +11548,7 @@
         <v>93</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34</v>
       </c>
       <c r="M55" s="12"/>
@@ -11403,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.8</v>
       </c>
       <c r="Q55" s="4">
@@ -11411,7 +11565,7 @@
         <v>93.600000000000023</v>
       </c>
       <c r="R55" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
       <c r="S55" s="25">
@@ -11423,7 +11577,7 @@
         <v>16.779661016949152</v>
       </c>
       <c r="U55" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.0677966101694913</v>
       </c>
       <c r="V55" s="12">
@@ -11461,7 +11615,10 @@
         <f t="shared" si="8"/>
         <v>40.5</v>
       </c>
-      <c r="AH55" s="12"/>
+      <c r="AH55" s="12">
+        <f t="shared" si="9"/>
+        <v>3.1860000000000004</v>
+      </c>
       <c r="AI55" s="12"/>
       <c r="AJ55" s="12"/>
       <c r="AK55" s="12"/>
@@ -11510,7 +11667,7 @@
         <v>127</v>
       </c>
       <c r="L56" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M56" s="12"/>
@@ -11519,11 +11676,11 @@
         <v>32</v>
       </c>
       <c r="P56" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>25.4</v>
       </c>
       <c r="Q56" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
       <c r="R56" s="4">
@@ -11536,7 +11693,7 @@
         <v>15</v>
       </c>
       <c r="U56" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.952755905511811</v>
       </c>
       <c r="V56" s="12">
@@ -11574,7 +11731,10 @@
         <f t="shared" si="8"/>
         <v>15.6</v>
       </c>
-      <c r="AH56" s="12"/>
+      <c r="AH56" s="12">
+        <f t="shared" si="9"/>
+        <v>7.6199999999999992</v>
+      </c>
       <c r="AI56" s="12"/>
       <c r="AJ56" s="12"/>
       <c r="AK56" s="12"/>
@@ -11625,7 +11785,7 @@
         <v>734</v>
       </c>
       <c r="L57" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-88</v>
       </c>
       <c r="M57" s="12"/>
@@ -11634,11 +11794,11 @@
         <v>701</v>
       </c>
       <c r="P57" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>129.19999999999999</v>
       </c>
       <c r="Q57" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>847.99999999999977</v>
       </c>
       <c r="R57" s="4">
@@ -11651,7 +11811,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="U57" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.4365325077399387</v>
       </c>
       <c r="V57" s="12">
@@ -11689,7 +11849,10 @@
         <f t="shared" si="8"/>
         <v>347.68</v>
       </c>
-      <c r="AH57" s="12"/>
+      <c r="AH57" s="12">
+        <f t="shared" si="9"/>
+        <v>52.971999999999994</v>
+      </c>
       <c r="AI57" s="12"/>
       <c r="AJ57" s="12"/>
       <c r="AK57" s="12"/>
@@ -11738,7 +11901,7 @@
         <v>432.4</v>
       </c>
       <c r="L58" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.314999999999998</v>
       </c>
       <c r="M58" s="12"/>
@@ -11747,11 +11910,11 @@
         <v>171</v>
       </c>
       <c r="P58" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>89.342999999999989</v>
       </c>
       <c r="Q58" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>471.81099999999981</v>
       </c>
       <c r="R58" s="4">
@@ -11767,7 +11930,7 @@
         <v>15.875155300359289</v>
       </c>
       <c r="U58" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.7191050222177449</v>
       </c>
       <c r="V58" s="12">
@@ -11805,7 +11968,10 @@
         <f t="shared" si="8"/>
         <v>550</v>
       </c>
-      <c r="AH58" s="12"/>
+      <c r="AH58" s="12">
+        <f t="shared" si="9"/>
+        <v>89.342999999999989</v>
+      </c>
       <c r="AI58" s="12"/>
       <c r="AJ58" s="12"/>
       <c r="AK58" s="12"/>
@@ -11854,7 +12020,7 @@
         <v>31</v>
       </c>
       <c r="L59" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M59" s="12"/>
@@ -11863,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.4</v>
       </c>
       <c r="Q59" s="4"/>
@@ -11877,7 +12043,7 @@
         <v>51.111111111111107</v>
       </c>
       <c r="U59" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>51.111111111111107</v>
       </c>
       <c r="V59" s="12">
@@ -11917,7 +12083,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="12"/>
+      <c r="AH59" s="12">
+        <f t="shared" si="9"/>
+        <v>1.89</v>
+      </c>
       <c r="AI59" s="12"/>
       <c r="AJ59" s="12"/>
       <c r="AK59" s="12"/>
@@ -11966,7 +12135,7 @@
         <v>63.2</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.9839999999999947</v>
       </c>
       <c r="M60" s="12"/>
@@ -11975,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.036799999999999</v>
       </c>
       <c r="Q60" s="4"/>
@@ -11989,7 +12158,7 @@
         <v>20.341034609720179</v>
       </c>
       <c r="U60" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.341034609720179</v>
       </c>
       <c r="V60" s="12">
@@ -12029,7 +12198,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH60" s="12"/>
+      <c r="AH60" s="12">
+        <f t="shared" si="9"/>
+        <v>13.036799999999999</v>
+      </c>
       <c r="AI60" s="12"/>
       <c r="AJ60" s="12"/>
       <c r="AK60" s="12"/>
@@ -12080,7 +12252,7 @@
         <v>404</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-48</v>
       </c>
       <c r="M61" s="12"/>
@@ -12089,11 +12261,11 @@
         <v>227</v>
       </c>
       <c r="P61" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>71.2</v>
       </c>
       <c r="Q61" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>425</v>
       </c>
       <c r="R61" s="4">
@@ -12106,7 +12278,7 @@
         <v>15</v>
       </c>
       <c r="U61" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.0308988764044944</v>
       </c>
       <c r="V61" s="12">
@@ -12144,7 +12316,10 @@
         <f t="shared" si="8"/>
         <v>174.25</v>
       </c>
-      <c r="AH61" s="12"/>
+      <c r="AH61" s="12">
+        <f t="shared" si="9"/>
+        <v>29.192</v>
+      </c>
       <c r="AI61" s="12"/>
       <c r="AJ61" s="12"/>
       <c r="AK61" s="12"/>
@@ -12193,7 +12368,7 @@
         <v>180.5</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.7539999999999907</v>
       </c>
       <c r="M62" s="12"/>
@@ -12202,15 +12377,15 @@
         <v>0</v>
       </c>
       <c r="P62" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>37.8508</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>311.44999999999993</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" ref="R62:R63" si="17">S62</f>
+        <f t="shared" ref="R62:R63" si="18">S62</f>
         <v>370</v>
       </c>
       <c r="S62" s="25">
@@ -12222,7 +12397,7 @@
         <v>16.546862946093611</v>
       </c>
       <c r="U62" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.7716402295327978</v>
       </c>
       <c r="V62" s="12">
@@ -12260,7 +12435,10 @@
         <f t="shared" si="8"/>
         <v>370</v>
       </c>
-      <c r="AH62" s="12"/>
+      <c r="AH62" s="12">
+        <f t="shared" si="9"/>
+        <v>37.8508</v>
+      </c>
       <c r="AI62" s="12"/>
       <c r="AJ62" s="12"/>
       <c r="AK62" s="12"/>
@@ -12311,7 +12489,7 @@
         <v>102</v>
       </c>
       <c r="L63" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-18</v>
       </c>
       <c r="M63" s="12"/>
@@ -12320,15 +12498,15 @@
         <v>165</v>
       </c>
       <c r="P63" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.8</v>
       </c>
       <c r="Q63" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
       <c r="R63" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>150</v>
       </c>
       <c r="S63" s="25">
@@ -12340,7 +12518,7 @@
         <v>21.726190476190474</v>
       </c>
       <c r="U63" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.797619047619047</v>
       </c>
       <c r="V63" s="12">
@@ -12378,7 +12556,10 @@
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="AH63" s="12"/>
+      <c r="AH63" s="12">
+        <f t="shared" si="9"/>
+        <v>5.04</v>
+      </c>
       <c r="AI63" s="12"/>
       <c r="AJ63" s="12"/>
       <c r="AK63" s="12"/>
@@ -12429,7 +12610,7 @@
         <v>251</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-61</v>
       </c>
       <c r="M64" s="12"/>
@@ -12438,7 +12619,7 @@
         <v>103</v>
       </c>
       <c r="P64" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="Q64" s="4"/>
@@ -12452,7 +12633,7 @@
         <v>15.263157894736842</v>
       </c>
       <c r="U64" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.263157894736842</v>
       </c>
       <c r="V64" s="12">
@@ -12490,7 +12671,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH64" s="12"/>
+      <c r="AH64" s="12">
+        <f t="shared" si="9"/>
+        <v>6.84</v>
+      </c>
       <c r="AI64" s="12"/>
       <c r="AJ64" s="12"/>
       <c r="AK64" s="12"/>
@@ -12539,7 +12723,7 @@
         <v>19</v>
       </c>
       <c r="L65" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M65" s="12"/>
@@ -12548,11 +12732,11 @@
         <v>20</v>
       </c>
       <c r="P65" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.8</v>
       </c>
       <c r="Q65" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
       <c r="R65" s="4">
@@ -12568,7 +12752,7 @@
         <v>19.736842105263158</v>
       </c>
       <c r="U65" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.5789473684210531</v>
       </c>
       <c r="V65" s="12">
@@ -12608,7 +12792,10 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="AH65" s="12"/>
+      <c r="AH65" s="12">
+        <f t="shared" si="9"/>
+        <v>0.83599999999999997</v>
+      </c>
       <c r="AI65" s="12"/>
       <c r="AJ65" s="12"/>
       <c r="AK65" s="12"/>
@@ -12657,7 +12844,7 @@
         <v>160</v>
       </c>
       <c r="L66" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M66" s="12"/>
@@ -12666,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>32.200000000000003</v>
       </c>
       <c r="Q66" s="4">
@@ -12683,7 +12870,7 @@
         <v>10</v>
       </c>
       <c r="U66" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9565217391304346</v>
       </c>
       <c r="V66" s="12">
@@ -12721,7 +12908,10 @@
         <f t="shared" si="8"/>
         <v>217.56</v>
       </c>
-      <c r="AH66" s="12"/>
+      <c r="AH66" s="12">
+        <f t="shared" si="9"/>
+        <v>27.048000000000002</v>
+      </c>
       <c r="AI66" s="12"/>
       <c r="AJ66" s="12"/>
       <c r="AK66" s="12"/>
@@ -12772,7 +12962,7 @@
         <v>438</v>
       </c>
       <c r="L67" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-17</v>
       </c>
       <c r="M67" s="12"/>
@@ -12781,15 +12971,15 @@
         <v>63</v>
       </c>
       <c r="P67" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84.2</v>
       </c>
       <c r="Q67" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>708</v>
       </c>
       <c r="R67" s="4">
-        <f t="shared" ref="R67:R68" si="18">S67</f>
+        <f t="shared" ref="R67:R68" si="19">S67</f>
         <v>800</v>
       </c>
       <c r="S67" s="25">
@@ -12801,7 +12991,7 @@
         <v>16.092636579572446</v>
       </c>
       <c r="U67" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.5914489311163891</v>
       </c>
       <c r="V67" s="12">
@@ -12839,7 +13029,10 @@
         <f t="shared" si="8"/>
         <v>280</v>
       </c>
-      <c r="AH67" s="12"/>
+      <c r="AH67" s="12">
+        <f t="shared" si="9"/>
+        <v>29.47</v>
+      </c>
       <c r="AI67" s="12"/>
       <c r="AJ67" s="12"/>
       <c r="AK67" s="12"/>
@@ -12888,7 +13081,7 @@
         <v>296</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-23</v>
       </c>
       <c r="M68" s="12"/>
@@ -12897,15 +13090,15 @@
         <v>50</v>
       </c>
       <c r="P68" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>54.6</v>
       </c>
       <c r="Q68" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>383</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>450</v>
       </c>
       <c r="S68" s="25">
@@ -12917,7 +13110,7 @@
         <v>16.227106227106226</v>
       </c>
       <c r="U68" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.9853479853479854</v>
       </c>
       <c r="V68" s="12">
@@ -12957,7 +13150,10 @@
         <f t="shared" si="8"/>
         <v>157.5</v>
       </c>
-      <c r="AH68" s="12"/>
+      <c r="AH68" s="12">
+        <f t="shared" si="9"/>
+        <v>19.11</v>
+      </c>
       <c r="AI68" s="12"/>
       <c r="AJ68" s="12"/>
       <c r="AK68" s="12"/>
@@ -13008,7 +13204,7 @@
         <v>252.5</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.021000000000015</v>
       </c>
       <c r="M69" s="12"/>
@@ -13017,11 +13213,11 @@
         <v>0</v>
       </c>
       <c r="P69" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>51.904200000000003</v>
       </c>
       <c r="Q69" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>274.5390000000001</v>
       </c>
       <c r="R69" s="4">
@@ -13034,7 +13230,7 @@
         <v>15.008881747527175</v>
       </c>
       <c r="U69" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.7106592530084264</v>
       </c>
       <c r="V69" s="12">
@@ -13072,7 +13268,10 @@
         <f t="shared" si="8"/>
         <v>275</v>
       </c>
-      <c r="AH69" s="12"/>
+      <c r="AH69" s="12">
+        <f t="shared" si="9"/>
+        <v>51.904200000000003</v>
+      </c>
       <c r="AI69" s="12"/>
       <c r="AJ69" s="12"/>
       <c r="AK69" s="12"/>
@@ -13123,7 +13322,7 @@
         <v>275.2</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
         <v>16.66700000000003</v>
       </c>
       <c r="M70" s="12"/>
@@ -13132,11 +13331,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="12">
-        <f t="shared" ref="P70:P105" si="20">E70/5</f>
+        <f t="shared" ref="P70:P105" si="21">E70/5</f>
         <v>58.373400000000004</v>
       </c>
       <c r="Q70" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>414.32900000000012</v>
       </c>
       <c r="R70" s="4">
@@ -13149,7 +13348,7 @@
         <v>14.994363871215311</v>
       </c>
       <c r="U70" s="12">
-        <f t="shared" ref="U70:U105" si="21">(F70+O70)/P70</f>
+        <f t="shared" ref="U70:U105" si="22">(F70+O70)/P70</f>
         <v>7.902092391397451</v>
       </c>
       <c r="V70" s="12">
@@ -13187,7 +13386,10 @@
         <f t="shared" si="8"/>
         <v>414</v>
       </c>
-      <c r="AH70" s="12"/>
+      <c r="AH70" s="12">
+        <f t="shared" si="9"/>
+        <v>58.373400000000004</v>
+      </c>
       <c r="AI70" s="12"/>
       <c r="AJ70" s="12"/>
       <c r="AK70" s="12"/>
@@ -13236,7 +13438,7 @@
         <v>243</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-19</v>
       </c>
       <c r="M71" s="12"/>
@@ -13245,11 +13447,11 @@
         <v>0</v>
       </c>
       <c r="P71" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>44.8</v>
       </c>
       <c r="Q71" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>143</v>
       </c>
       <c r="R71" s="4">
@@ -13261,11 +13463,11 @@
         <v>200</v>
       </c>
       <c r="T71" s="12">
-        <f t="shared" ref="T71:T105" si="22">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="T71:T105" si="23">(F71+O71+R71)/P71</f>
         <v>16.272321428571431</v>
       </c>
       <c r="U71" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.808035714285715</v>
       </c>
       <c r="V71" s="12">
@@ -13300,10 +13502,13 @@
       </c>
       <c r="AF71" s="12"/>
       <c r="AG71" s="12">
-        <f t="shared" ref="AG71:AG105" si="23">G71*R71</f>
+        <f t="shared" ref="AG71:AG105" si="24">G71*R71</f>
         <v>70</v>
       </c>
-      <c r="AH71" s="12"/>
+      <c r="AH71" s="12">
+        <f t="shared" ref="AH71:AH105" si="25">P71*G71</f>
+        <v>15.679999999999998</v>
+      </c>
       <c r="AI71" s="12"/>
       <c r="AJ71" s="12"/>
       <c r="AK71" s="12"/>
@@ -13352,7 +13557,7 @@
         <v>76</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-8</v>
       </c>
       <c r="M72" s="12"/>
@@ -13361,7 +13566,7 @@
         <v>15</v>
       </c>
       <c r="P72" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.6</v>
       </c>
       <c r="Q72" s="4">
@@ -13369,16 +13574,16 @@
         <v>107.4</v>
       </c>
       <c r="R72" s="4">
-        <f t="shared" ref="R72:R105" si="24">ROUND(Q72,0)</f>
+        <f t="shared" ref="R72:R105" si="26">ROUND(Q72,0)</f>
         <v>107</v>
       </c>
       <c r="S72" s="25"/>
       <c r="T72" s="12">
+        <f t="shared" si="23"/>
+        <v>13.970588235294118</v>
+      </c>
+      <c r="U72" s="12">
         <f t="shared" si="22"/>
-        <v>13.970588235294118</v>
-      </c>
-      <c r="U72" s="12">
-        <f t="shared" si="21"/>
         <v>6.1029411764705888</v>
       </c>
       <c r="V72" s="12">
@@ -13413,10 +13618,13 @@
       </c>
       <c r="AF72" s="12"/>
       <c r="AG72" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32.1</v>
       </c>
-      <c r="AH72" s="12"/>
+      <c r="AH72" s="12">
+        <f t="shared" si="25"/>
+        <v>4.08</v>
+      </c>
       <c r="AI72" s="12"/>
       <c r="AJ72" s="12"/>
       <c r="AK72" s="12"/>
@@ -13465,7 +13673,7 @@
         <v>86</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="M73" s="12"/>
@@ -13474,61 +13682,64 @@
         <v>0</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.2</v>
       </c>
       <c r="Q73" s="4"/>
       <c r="R73" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="25"/>
+      <c r="T73" s="12">
+        <f t="shared" si="23"/>
+        <v>16.381578947368421</v>
+      </c>
+      <c r="U73" s="12">
+        <f t="shared" si="22"/>
+        <v>16.381578947368421</v>
+      </c>
+      <c r="V73" s="12">
+        <v>16</v>
+      </c>
+      <c r="W73" s="12">
+        <v>9.4</v>
+      </c>
+      <c r="X73" s="12">
+        <v>22</v>
+      </c>
+      <c r="Y73" s="12">
+        <v>10.4</v>
+      </c>
+      <c r="Z73" s="12">
+        <v>19</v>
+      </c>
+      <c r="AA73" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AB73" s="12">
+        <v>15.6</v>
+      </c>
+      <c r="AC73" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AD73" s="12">
+        <v>17.2</v>
+      </c>
+      <c r="AE73" s="12">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AF73" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG73" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S73" s="25"/>
-      <c r="T73" s="12">
-        <f t="shared" si="22"/>
-        <v>16.381578947368421</v>
-      </c>
-      <c r="U73" s="12">
-        <f t="shared" si="21"/>
-        <v>16.381578947368421</v>
-      </c>
-      <c r="V73" s="12">
-        <v>16</v>
-      </c>
-      <c r="W73" s="12">
-        <v>9.4</v>
-      </c>
-      <c r="X73" s="12">
-        <v>22</v>
-      </c>
-      <c r="Y73" s="12">
-        <v>10.4</v>
-      </c>
-      <c r="Z73" s="12">
-        <v>19</v>
-      </c>
-      <c r="AA73" s="12">
-        <v>16.2</v>
-      </c>
-      <c r="AB73" s="12">
-        <v>15.6</v>
-      </c>
-      <c r="AC73" s="12">
-        <v>16.2</v>
-      </c>
-      <c r="AD73" s="12">
-        <v>17.2</v>
-      </c>
-      <c r="AE73" s="12">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="AF73" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG73" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH73" s="12"/>
+      <c r="AH73" s="12">
+        <f t="shared" si="25"/>
+        <v>4.5599999999999996</v>
+      </c>
       <c r="AI73" s="12"/>
       <c r="AJ73" s="12"/>
       <c r="AK73" s="12"/>
@@ -13579,7 +13790,7 @@
         <v>165</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M74" s="12"/>
@@ -13588,15 +13799,15 @@
         <v>0</v>
       </c>
       <c r="P74" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>32</v>
       </c>
       <c r="Q74" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>230</v>
       </c>
       <c r="R74" s="4">
-        <f t="shared" ref="R74:R75" si="25">S74</f>
+        <f t="shared" ref="R74:R75" si="27">S74</f>
         <v>350</v>
       </c>
       <c r="S74" s="25">
@@ -13604,11 +13815,11 @@
         <v>350</v>
       </c>
       <c r="T74" s="12">
+        <f t="shared" si="23"/>
+        <v>18.75</v>
+      </c>
+      <c r="U74" s="12">
         <f t="shared" si="22"/>
-        <v>18.75</v>
-      </c>
-      <c r="U74" s="12">
-        <f t="shared" si="21"/>
         <v>7.8125</v>
       </c>
       <c r="V74" s="12">
@@ -13643,10 +13854,13 @@
       </c>
       <c r="AF74" s="12"/>
       <c r="AG74" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>98.000000000000014</v>
       </c>
-      <c r="AH74" s="12"/>
+      <c r="AH74" s="12">
+        <f t="shared" si="25"/>
+        <v>8.9600000000000009</v>
+      </c>
       <c r="AI74" s="12"/>
       <c r="AJ74" s="12"/>
       <c r="AK74" s="12"/>
@@ -13695,7 +13909,7 @@
         <v>196</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-12</v>
       </c>
       <c r="M75" s="12"/>
@@ -13704,7 +13918,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.799999999999997</v>
       </c>
       <c r="Q75" s="4">
@@ -13712,7 +13926,7 @@
         <v>311.19999999999993</v>
       </c>
       <c r="R75" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>400</v>
       </c>
       <c r="S75" s="25">
@@ -13720,11 +13934,11 @@
         <v>400</v>
       </c>
       <c r="T75" s="12">
+        <f t="shared" si="23"/>
+        <v>16.413043478260871</v>
+      </c>
+      <c r="U75" s="12">
         <f t="shared" si="22"/>
-        <v>16.413043478260871</v>
-      </c>
-      <c r="U75" s="12">
-        <f t="shared" si="21"/>
         <v>5.5434782608695654</v>
       </c>
       <c r="V75" s="12">
@@ -13759,10 +13973,13 @@
       </c>
       <c r="AF75" s="12"/>
       <c r="AG75" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>112.00000000000001</v>
       </c>
-      <c r="AH75" s="12"/>
+      <c r="AH75" s="12">
+        <f t="shared" si="25"/>
+        <v>10.304</v>
+      </c>
       <c r="AI75" s="12"/>
       <c r="AJ75" s="12"/>
       <c r="AK75" s="12"/>
@@ -13813,7 +14030,7 @@
         <v>535</v>
       </c>
       <c r="L76" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-48</v>
       </c>
       <c r="M76" s="12"/>
@@ -13822,24 +14039,24 @@
         <v>540</v>
       </c>
       <c r="P76" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>97.4</v>
       </c>
       <c r="Q76" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>649</v>
       </c>
       <c r="R76" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>649</v>
       </c>
       <c r="S76" s="25"/>
       <c r="T76" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U76" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U76" s="12">
-        <f t="shared" si="21"/>
         <v>8.3367556468172488</v>
       </c>
       <c r="V76" s="12">
@@ -13874,10 +14091,13 @@
       </c>
       <c r="AF76" s="12"/>
       <c r="AG76" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>181.72000000000003</v>
       </c>
-      <c r="AH76" s="12"/>
+      <c r="AH76" s="12">
+        <f t="shared" si="25"/>
+        <v>27.272000000000006</v>
+      </c>
       <c r="AI76" s="12"/>
       <c r="AJ76" s="12"/>
       <c r="AK76" s="12"/>
@@ -13926,7 +14146,7 @@
         <v>160</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-3</v>
       </c>
       <c r="M77" s="12"/>
@@ -13935,24 +14155,24 @@
         <v>0</v>
       </c>
       <c r="P77" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>31.4</v>
       </c>
       <c r="Q77" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>171</v>
       </c>
       <c r="R77" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>171</v>
       </c>
       <c r="S77" s="25"/>
       <c r="T77" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U77" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U77" s="12">
-        <f t="shared" si="21"/>
         <v>9.5541401273885356</v>
       </c>
       <c r="V77" s="12">
@@ -13987,10 +14207,13 @@
       </c>
       <c r="AF77" s="12"/>
       <c r="AG77" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>68.400000000000006</v>
       </c>
-      <c r="AH77" s="12"/>
+      <c r="AH77" s="12">
+        <f t="shared" si="25"/>
+        <v>12.56</v>
+      </c>
       <c r="AI77" s="12"/>
       <c r="AJ77" s="12"/>
       <c r="AK77" s="12"/>
@@ -14041,7 +14264,7 @@
         <v>95.4</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-68.324000000000012</v>
       </c>
       <c r="M78" s="12"/>
@@ -14050,7 +14273,7 @@
         <v>423</v>
       </c>
       <c r="P78" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.4152000000000005</v>
       </c>
       <c r="Q78" s="4"/>
@@ -14062,11 +14285,11 @@
         <v>500</v>
       </c>
       <c r="T78" s="12">
+        <f t="shared" si="23"/>
+        <v>151.40253360910029</v>
+      </c>
+      <c r="U78" s="12">
         <f t="shared" si="22"/>
-        <v>151.40253360910029</v>
-      </c>
-      <c r="U78" s="12">
-        <f t="shared" si="21"/>
         <v>77.536379081105025</v>
       </c>
       <c r="V78" s="12">
@@ -14103,10 +14326,13 @@
         <v>58</v>
       </c>
       <c r="AG78" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>400</v>
       </c>
-      <c r="AH78" s="12"/>
+      <c r="AH78" s="12">
+        <f t="shared" si="25"/>
+        <v>5.4152000000000005</v>
+      </c>
       <c r="AI78" s="12"/>
       <c r="AJ78" s="12"/>
       <c r="AK78" s="12"/>
@@ -14155,7 +14381,7 @@
         <v>15</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M79" s="12"/>
@@ -14164,15 +14390,15 @@
         <v>0</v>
       </c>
       <c r="P79" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="Q79" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" ref="R79" si="26">S79</f>
+        <f t="shared" ref="R79" si="28">S79</f>
         <v>30</v>
       </c>
       <c r="S79" s="25">
@@ -14180,11 +14406,11 @@
         <v>30</v>
       </c>
       <c r="T79" s="12">
+        <f t="shared" si="23"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U79" s="12">
         <f t="shared" si="22"/>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="U79" s="12">
-        <f t="shared" si="21"/>
         <v>10.333333333333334</v>
       </c>
       <c r="V79" s="12">
@@ -14221,10 +14447,13 @@
         <v>112</v>
       </c>
       <c r="AG79" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.14</v>
       </c>
-      <c r="AH79" s="12"/>
+      <c r="AH79" s="12">
+        <f t="shared" si="25"/>
+        <v>1.014</v>
+      </c>
       <c r="AI79" s="12"/>
       <c r="AJ79" s="12"/>
       <c r="AK79" s="12"/>
@@ -14273,7 +14502,7 @@
         <v>18</v>
       </c>
       <c r="L80" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M80" s="12"/>
@@ -14282,61 +14511,64 @@
         <v>0</v>
       </c>
       <c r="P80" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.6</v>
       </c>
       <c r="Q80" s="4"/>
       <c r="R80" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S80" s="25"/>
+      <c r="T80" s="12">
+        <f t="shared" si="23"/>
+        <v>19.722222222222221</v>
+      </c>
+      <c r="U80" s="12">
+        <f t="shared" si="22"/>
+        <v>19.722222222222221</v>
+      </c>
+      <c r="V80" s="12">
+        <v>0</v>
+      </c>
+      <c r="W80" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="X80" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG80" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S80" s="25"/>
-      <c r="T80" s="12">
-        <f t="shared" si="22"/>
-        <v>19.722222222222221</v>
-      </c>
-      <c r="U80" s="12">
-        <f t="shared" si="21"/>
-        <v>19.722222222222221</v>
-      </c>
-      <c r="V80" s="12">
-        <v>0</v>
-      </c>
-      <c r="W80" s="12">
-        <v>3.6</v>
-      </c>
-      <c r="X80" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG80" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH80" s="12"/>
+      <c r="AH80" s="12">
+        <f t="shared" si="25"/>
+        <v>1.1700000000000002</v>
+      </c>
       <c r="AI80" s="12"/>
       <c r="AJ80" s="12"/>
       <c r="AK80" s="12"/>
@@ -14387,7 +14619,7 @@
         <v>118</v>
       </c>
       <c r="L81" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-21</v>
       </c>
       <c r="M81" s="12"/>
@@ -14396,61 +14628,64 @@
         <v>0</v>
       </c>
       <c r="P81" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19.399999999999999</v>
       </c>
       <c r="Q81" s="4"/>
       <c r="R81" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S81" s="25"/>
+      <c r="T81" s="12">
+        <f t="shared" si="23"/>
+        <v>31.134020618556704</v>
+      </c>
+      <c r="U81" s="12">
+        <f t="shared" si="22"/>
+        <v>31.134020618556704</v>
+      </c>
+      <c r="V81" s="12">
+        <v>24.2</v>
+      </c>
+      <c r="W81" s="12">
+        <v>28.2</v>
+      </c>
+      <c r="X81" s="12">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="Y81" s="12">
+        <v>20.6</v>
+      </c>
+      <c r="Z81" s="12">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AA81" s="12">
+        <v>42.4</v>
+      </c>
+      <c r="AB81" s="12">
+        <v>23.8</v>
+      </c>
+      <c r="AC81" s="12">
+        <v>27.4</v>
+      </c>
+      <c r="AD81" s="12">
+        <v>28.2</v>
+      </c>
+      <c r="AE81" s="12">
+        <v>22.2</v>
+      </c>
+      <c r="AF81" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG81" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S81" s="25"/>
-      <c r="T81" s="12">
-        <f t="shared" si="22"/>
-        <v>31.134020618556704</v>
-      </c>
-      <c r="U81" s="12">
-        <f t="shared" si="21"/>
-        <v>31.134020618556704</v>
-      </c>
-      <c r="V81" s="12">
-        <v>24.2</v>
-      </c>
-      <c r="W81" s="12">
-        <v>28.2</v>
-      </c>
-      <c r="X81" s="12">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="Y81" s="12">
-        <v>20.6</v>
-      </c>
-      <c r="Z81" s="12">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="AA81" s="12">
-        <v>42.4</v>
-      </c>
-      <c r="AB81" s="12">
-        <v>23.8</v>
-      </c>
-      <c r="AC81" s="12">
-        <v>27.4</v>
-      </c>
-      <c r="AD81" s="12">
-        <v>28.2</v>
-      </c>
-      <c r="AE81" s="12">
-        <v>22.2</v>
-      </c>
-      <c r="AF81" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG81" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH81" s="12"/>
+      <c r="AH81" s="12">
+        <f t="shared" si="25"/>
+        <v>2.3279999999999998</v>
+      </c>
       <c r="AI81" s="12"/>
       <c r="AJ81" s="12"/>
       <c r="AK81" s="12"/>
@@ -14499,7 +14734,7 @@
         <v>125</v>
       </c>
       <c r="L82" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-14</v>
       </c>
       <c r="M82" s="12"/>
@@ -14508,7 +14743,7 @@
         <v>69</v>
       </c>
       <c r="P82" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.2</v>
       </c>
       <c r="Q82" s="4">
@@ -14516,16 +14751,16 @@
         <v>171.8</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>172</v>
       </c>
       <c r="S82" s="25"/>
       <c r="T82" s="12">
+        <f t="shared" si="23"/>
+        <v>14.009009009009009</v>
+      </c>
+      <c r="U82" s="12">
         <f t="shared" si="22"/>
-        <v>14.009009009009009</v>
-      </c>
-      <c r="U82" s="12">
-        <f t="shared" si="21"/>
         <v>6.2612612612612617</v>
       </c>
       <c r="V82" s="12">
@@ -14562,10 +14797,13 @@
         <v>112</v>
       </c>
       <c r="AG82" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25.8</v>
       </c>
-      <c r="AH82" s="12"/>
+      <c r="AH82" s="12">
+        <f t="shared" si="25"/>
+        <v>3.3299999999999996</v>
+      </c>
       <c r="AI82" s="12"/>
       <c r="AJ82" s="12"/>
       <c r="AK82" s="12"/>
@@ -14606,7 +14844,7 @@
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
       <c r="L83" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M83" s="8"/>
@@ -14615,61 +14853,64 @@
         <v>120</v>
       </c>
       <c r="P83" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S83" s="25"/>
+      <c r="T83" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U83" s="8" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V83" s="8">
+        <v>0</v>
+      </c>
+      <c r="W83" s="8">
+        <v>0</v>
+      </c>
+      <c r="X83" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG83" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S83" s="25"/>
-      <c r="T83" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U83" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V83" s="8">
+      <c r="AH83" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W83" s="8">
-        <v>0</v>
-      </c>
-      <c r="X83" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG83" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH83" s="12"/>
       <c r="AI83" s="12"/>
       <c r="AJ83" s="12"/>
       <c r="AK83" s="12"/>
@@ -14720,7 +14961,7 @@
         <v>80</v>
       </c>
       <c r="L84" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M84" s="12"/>
@@ -14729,24 +14970,24 @@
         <v>66</v>
       </c>
       <c r="P84" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.8</v>
       </c>
       <c r="Q84" s="4">
-        <f t="shared" ref="Q84:Q86" si="27">15*P84-O84-F84</f>
+        <f t="shared" ref="Q84:Q86" si="29">15*P84-O84-F84</f>
         <v>122</v>
       </c>
       <c r="R84" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>122</v>
       </c>
       <c r="S84" s="25"/>
       <c r="T84" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U84" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U84" s="12">
-        <f t="shared" si="21"/>
         <v>7.2784810126582276</v>
       </c>
       <c r="V84" s="12">
@@ -14783,10 +15024,13 @@
         <v>112</v>
       </c>
       <c r="AG84" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.3</v>
       </c>
-      <c r="AH84" s="12"/>
+      <c r="AH84" s="12">
+        <f t="shared" si="25"/>
+        <v>2.37</v>
+      </c>
       <c r="AI84" s="12"/>
       <c r="AJ84" s="12"/>
       <c r="AK84" s="12"/>
@@ -14837,7 +15081,7 @@
         <v>106</v>
       </c>
       <c r="L85" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-12</v>
       </c>
       <c r="M85" s="12"/>
@@ -14846,7 +15090,7 @@
         <v>55</v>
       </c>
       <c r="P85" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>18.8</v>
       </c>
       <c r="Q85" s="4">
@@ -14862,11 +15106,11 @@
         <v>250</v>
       </c>
       <c r="T85" s="12">
+        <f t="shared" si="23"/>
+        <v>17.819148936170212</v>
+      </c>
+      <c r="U85" s="12">
         <f t="shared" si="22"/>
-        <v>17.819148936170212</v>
-      </c>
-      <c r="U85" s="12">
-        <f t="shared" si="21"/>
         <v>4.5212765957446805</v>
       </c>
       <c r="V85" s="12">
@@ -14901,10 +15145,13 @@
       </c>
       <c r="AF85" s="12"/>
       <c r="AG85" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>82.5</v>
       </c>
-      <c r="AH85" s="12"/>
+      <c r="AH85" s="12">
+        <f t="shared" si="25"/>
+        <v>6.2040000000000006</v>
+      </c>
       <c r="AI85" s="12"/>
       <c r="AJ85" s="12"/>
       <c r="AK85" s="12"/>
@@ -14955,7 +15202,7 @@
         <v>296</v>
       </c>
       <c r="L86" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-15</v>
       </c>
       <c r="M86" s="12"/>
@@ -14964,24 +15211,24 @@
         <v>325</v>
       </c>
       <c r="P86" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>56.2</v>
       </c>
       <c r="Q86" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>253</v>
       </c>
       <c r="R86" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>253</v>
       </c>
       <c r="S86" s="25"/>
       <c r="T86" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U86" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U86" s="12">
-        <f t="shared" si="21"/>
         <v>10.498220640569395</v>
       </c>
       <c r="V86" s="12">
@@ -15016,10 +15263,13 @@
       </c>
       <c r="AF86" s="12"/>
       <c r="AG86" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>37.949999999999996</v>
       </c>
-      <c r="AH86" s="12"/>
+      <c r="AH86" s="12">
+        <f t="shared" si="25"/>
+        <v>8.43</v>
+      </c>
       <c r="AI86" s="12"/>
       <c r="AJ86" s="12"/>
       <c r="AK86" s="12"/>
@@ -15060,7 +15310,7 @@
       <c r="J87" s="13"/>
       <c r="K87" s="13"/>
       <c r="L87" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M87" s="13"/>
@@ -15069,61 +15319,64 @@
         <v>0</v>
       </c>
       <c r="P87" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q87" s="15"/>
       <c r="R87" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S87" s="25"/>
+      <c r="T87" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U87" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V87" s="13">
+        <v>0</v>
+      </c>
+      <c r="W87" s="13">
+        <v>0</v>
+      </c>
+      <c r="X87" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG87" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S87" s="25"/>
-      <c r="T87" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U87" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V87" s="13">
+      <c r="AH87" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W87" s="13">
-        <v>0</v>
-      </c>
-      <c r="X87" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE87" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF87" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH87" s="12"/>
       <c r="AI87" s="12"/>
       <c r="AJ87" s="12"/>
       <c r="AK87" s="12"/>
@@ -15164,7 +15417,7 @@
       <c r="J88" s="13"/>
       <c r="K88" s="13"/>
       <c r="L88" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M88" s="13"/>
@@ -15173,61 +15426,64 @@
         <v>0</v>
       </c>
       <c r="P88" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q88" s="15"/>
       <c r="R88" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S88" s="25"/>
+      <c r="T88" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U88" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V88" s="13">
+        <v>0</v>
+      </c>
+      <c r="W88" s="13">
+        <v>0</v>
+      </c>
+      <c r="X88" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="13">
+        <v>1.3322000000000001</v>
+      </c>
+      <c r="AA88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG88" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S88" s="25"/>
-      <c r="T88" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U88" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V88" s="13">
+      <c r="AH88" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W88" s="13">
-        <v>0</v>
-      </c>
-      <c r="X88" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="13">
-        <v>1.3322000000000001</v>
-      </c>
-      <c r="AA88" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC88" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF88" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG88" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH88" s="12"/>
       <c r="AI88" s="12"/>
       <c r="AJ88" s="12"/>
       <c r="AK88" s="12"/>
@@ -15268,7 +15524,7 @@
       <c r="J89" s="13"/>
       <c r="K89" s="13"/>
       <c r="L89" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M89" s="13"/>
@@ -15277,61 +15533,64 @@
         <v>0</v>
       </c>
       <c r="P89" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q89" s="15"/>
       <c r="R89" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S89" s="25"/>
+      <c r="T89" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U89" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V89" s="13">
+        <v>0</v>
+      </c>
+      <c r="W89" s="13">
+        <v>0</v>
+      </c>
+      <c r="X89" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG89" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S89" s="25"/>
-      <c r="T89" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U89" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V89" s="13">
+      <c r="AH89" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W89" s="13">
-        <v>0</v>
-      </c>
-      <c r="X89" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH89" s="12"/>
       <c r="AI89" s="12"/>
       <c r="AJ89" s="12"/>
       <c r="AK89" s="12"/>
@@ -15374,7 +15633,7 @@
       <c r="J90" s="13"/>
       <c r="K90" s="13"/>
       <c r="L90" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-2.1659999999999999</v>
       </c>
       <c r="M90" s="13"/>
@@ -15383,61 +15642,64 @@
         <v>0</v>
       </c>
       <c r="P90" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.43319999999999997</v>
       </c>
       <c r="Q90" s="15"/>
       <c r="R90" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S90" s="25"/>
+      <c r="T90" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="V90" s="13">
+        <v>0</v>
+      </c>
+      <c r="W90" s="13">
+        <v>0</v>
+      </c>
+      <c r="X90" s="13">
+        <v>0.28539999999999999</v>
+      </c>
+      <c r="Y90" s="13">
+        <v>0.59400000000000008</v>
+      </c>
+      <c r="Z90" s="13">
+        <v>0.86319999999999997</v>
+      </c>
+      <c r="AA90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG90" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S90" s="25"/>
-      <c r="T90" s="12">
-        <f t="shared" si="22"/>
+      <c r="AH90" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U90" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="13">
-        <v>0</v>
-      </c>
-      <c r="W90" s="13">
-        <v>0</v>
-      </c>
-      <c r="X90" s="13">
-        <v>0.28539999999999999</v>
-      </c>
-      <c r="Y90" s="13">
-        <v>0.59400000000000008</v>
-      </c>
-      <c r="Z90" s="13">
-        <v>0.86319999999999997</v>
-      </c>
-      <c r="AA90" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD90" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF90" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG90" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH90" s="12"/>
       <c r="AI90" s="12"/>
       <c r="AJ90" s="12"/>
       <c r="AK90" s="12"/>
@@ -15488,7 +15750,7 @@
         <v>133</v>
       </c>
       <c r="L91" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
       <c r="M91" s="12"/>
@@ -15497,7 +15759,7 @@
         <v>103</v>
       </c>
       <c r="P91" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24.4</v>
       </c>
       <c r="Q91" s="4">
@@ -15505,16 +15767,16 @@
         <v>169</v>
       </c>
       <c r="R91" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>169</v>
       </c>
       <c r="S91" s="25"/>
       <c r="T91" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U91" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U91" s="12">
-        <f t="shared" si="21"/>
         <v>8.0737704918032787</v>
       </c>
       <c r="V91" s="12">
@@ -15549,10 +15811,13 @@
       </c>
       <c r="AF91" s="12"/>
       <c r="AG91" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>67.600000000000009</v>
       </c>
-      <c r="AH91" s="12"/>
+      <c r="AH91" s="12">
+        <f t="shared" si="25"/>
+        <v>9.76</v>
+      </c>
       <c r="AI91" s="12"/>
       <c r="AJ91" s="12"/>
       <c r="AK91" s="12"/>
@@ -15595,7 +15860,7 @@
         <v>9</v>
       </c>
       <c r="L92" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-9</v>
       </c>
       <c r="M92" s="13"/>
@@ -15604,61 +15869,64 @@
         <v>0</v>
       </c>
       <c r="P92" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q92" s="15"/>
       <c r="R92" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S92" s="25"/>
+      <c r="T92" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U92" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V92" s="13">
+        <v>0</v>
+      </c>
+      <c r="W92" s="13">
+        <v>0</v>
+      </c>
+      <c r="X92" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="AB92" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="AC92" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="AD92" s="13">
+        <v>2.4</v>
+      </c>
+      <c r="AE92" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="AF92" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG92" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S92" s="25"/>
-      <c r="T92" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U92" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V92" s="13">
+      <c r="AH92" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W92" s="13">
-        <v>0</v>
-      </c>
-      <c r="X92" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="AB92" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="AC92" s="13">
-        <v>1.6</v>
-      </c>
-      <c r="AD92" s="13">
-        <v>2.4</v>
-      </c>
-      <c r="AE92" s="13">
-        <v>2.8</v>
-      </c>
-      <c r="AF92" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG92" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="12"/>
       <c r="AI92" s="12"/>
       <c r="AJ92" s="12"/>
       <c r="AK92" s="12"/>
@@ -15699,7 +15967,7 @@
       <c r="J93" s="13"/>
       <c r="K93" s="13"/>
       <c r="L93" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M93" s="13"/>
@@ -15708,61 +15976,64 @@
         <v>0</v>
       </c>
       <c r="P93" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q93" s="15"/>
       <c r="R93" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S93" s="25"/>
+      <c r="T93" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U93" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V93" s="13">
+        <v>0</v>
+      </c>
+      <c r="W93" s="13">
+        <v>0</v>
+      </c>
+      <c r="X93" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG93" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S93" s="25"/>
-      <c r="T93" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U93" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V93" s="13">
+      <c r="AH93" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W93" s="13">
-        <v>0</v>
-      </c>
-      <c r="X93" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE93" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF93" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG93" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH93" s="12"/>
       <c r="AI93" s="12"/>
       <c r="AJ93" s="12"/>
       <c r="AK93" s="12"/>
@@ -15801,7 +16072,7 @@
       <c r="J94" s="13"/>
       <c r="K94" s="13"/>
       <c r="L94" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M94" s="13"/>
@@ -15810,61 +16081,64 @@
         <v>0</v>
       </c>
       <c r="P94" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q94" s="15"/>
       <c r="R94" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S94" s="25"/>
+      <c r="T94" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U94" s="13" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V94" s="13">
+        <v>0</v>
+      </c>
+      <c r="W94" s="13">
+        <v>0</v>
+      </c>
+      <c r="X94" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG94" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S94" s="25"/>
-      <c r="T94" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U94" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V94" s="13">
+      <c r="AH94" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W94" s="13">
-        <v>0</v>
-      </c>
-      <c r="X94" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG94" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH94" s="12"/>
       <c r="AI94" s="12"/>
       <c r="AJ94" s="12"/>
       <c r="AK94" s="12"/>
@@ -15913,7 +16187,7 @@
         <v>75</v>
       </c>
       <c r="L95" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M95" s="12"/>
@@ -15922,59 +16196,62 @@
         <v>0</v>
       </c>
       <c r="P95" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
       <c r="Q95" s="4"/>
       <c r="R95" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S95" s="25"/>
+      <c r="T95" s="12">
+        <f t="shared" si="23"/>
+        <v>15.357142857142858</v>
+      </c>
+      <c r="U95" s="12">
+        <f t="shared" si="22"/>
+        <v>15.357142857142858</v>
+      </c>
+      <c r="V95" s="12">
+        <v>11.2</v>
+      </c>
+      <c r="W95" s="12">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X95" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="Y95" s="12">
+        <v>34</v>
+      </c>
+      <c r="Z95" s="12">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AA95" s="12">
+        <v>15.2</v>
+      </c>
+      <c r="AB95" s="12">
+        <v>10.4</v>
+      </c>
+      <c r="AC95" s="12">
+        <v>19.8</v>
+      </c>
+      <c r="AD95" s="12">
+        <v>18</v>
+      </c>
+      <c r="AE95" s="12">
+        <v>14.6</v>
+      </c>
+      <c r="AF95" s="12"/>
+      <c r="AG95" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S95" s="25"/>
-      <c r="T95" s="12">
-        <f t="shared" si="22"/>
-        <v>15.357142857142858</v>
-      </c>
-      <c r="U95" s="12">
-        <f t="shared" si="21"/>
-        <v>15.357142857142858</v>
-      </c>
-      <c r="V95" s="12">
-        <v>11.2</v>
-      </c>
-      <c r="W95" s="12">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="X95" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="Y95" s="12">
-        <v>34</v>
-      </c>
-      <c r="Z95" s="12">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AA95" s="12">
-        <v>15.2</v>
-      </c>
-      <c r="AB95" s="12">
-        <v>10.4</v>
-      </c>
-      <c r="AC95" s="12">
-        <v>19.8</v>
-      </c>
-      <c r="AD95" s="12">
-        <v>18</v>
-      </c>
-      <c r="AE95" s="12">
-        <v>14.6</v>
-      </c>
-      <c r="AF95" s="12"/>
-      <c r="AG95" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH95" s="12"/>
+      <c r="AH95" s="12">
+        <f t="shared" si="25"/>
+        <v>4.62</v>
+      </c>
       <c r="AI95" s="12"/>
       <c r="AJ95" s="12"/>
       <c r="AK95" s="12"/>
@@ -16025,7 +16302,7 @@
         <v>252</v>
       </c>
       <c r="L96" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-25</v>
       </c>
       <c r="M96" s="12"/>
@@ -16034,15 +16311,15 @@
         <v>128</v>
       </c>
       <c r="P96" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>45.4</v>
       </c>
       <c r="Q96" s="4">
-        <f t="shared" ref="Q96" si="28">15*P96-O96-F96</f>
+        <f t="shared" ref="Q96" si="30">15*P96-O96-F96</f>
         <v>163</v>
       </c>
       <c r="R96" s="4">
-        <f t="shared" ref="R96:R98" si="29">S96</f>
+        <f t="shared" ref="R96:R98" si="31">S96</f>
         <v>200</v>
       </c>
       <c r="S96" s="25">
@@ -16050,11 +16327,11 @@
         <v>200</v>
       </c>
       <c r="T96" s="12">
+        <f t="shared" si="23"/>
+        <v>15.814977973568283</v>
+      </c>
+      <c r="U96" s="12">
         <f t="shared" si="22"/>
-        <v>15.814977973568283</v>
-      </c>
-      <c r="U96" s="12">
-        <f t="shared" si="21"/>
         <v>11.409691629955947</v>
       </c>
       <c r="V96" s="12">
@@ -16089,10 +16366,13 @@
       </c>
       <c r="AF96" s="12"/>
       <c r="AG96" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
-      <c r="AH96" s="12"/>
+      <c r="AH96" s="12">
+        <f t="shared" si="25"/>
+        <v>4.54</v>
+      </c>
       <c r="AI96" s="12"/>
       <c r="AJ96" s="12"/>
       <c r="AK96" s="12"/>
@@ -16143,7 +16423,7 @@
         <v>192</v>
       </c>
       <c r="L97" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="M97" s="12"/>
@@ -16152,7 +16432,7 @@
         <v>699</v>
       </c>
       <c r="P97" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.4</v>
       </c>
       <c r="Q97" s="4"/>
@@ -16164,11 +16444,11 @@
         <v>150</v>
       </c>
       <c r="T97" s="12">
+        <f t="shared" si="23"/>
+        <v>25.631868131868131</v>
+      </c>
+      <c r="U97" s="12">
         <f t="shared" si="22"/>
-        <v>25.631868131868131</v>
-      </c>
-      <c r="U97" s="12">
-        <f t="shared" si="21"/>
         <v>22.884615384615387</v>
       </c>
       <c r="V97" s="12">
@@ -16203,10 +16483,13 @@
       </c>
       <c r="AF97" s="12"/>
       <c r="AG97" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
-      <c r="AH97" s="12"/>
+      <c r="AH97" s="12">
+        <f t="shared" si="25"/>
+        <v>3.64</v>
+      </c>
       <c r="AI97" s="12"/>
       <c r="AJ97" s="12"/>
       <c r="AK97" s="12"/>
@@ -16255,7 +16538,7 @@
         <v>125</v>
       </c>
       <c r="L98" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-3</v>
       </c>
       <c r="M98" s="12"/>
@@ -16264,12 +16547,12 @@
         <v>169</v>
       </c>
       <c r="P98" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24.4</v>
       </c>
       <c r="Q98" s="4"/>
       <c r="R98" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>100</v>
       </c>
       <c r="S98" s="25">
@@ -16277,11 +16560,11 @@
         <v>100</v>
       </c>
       <c r="T98" s="12">
+        <f t="shared" si="23"/>
+        <v>19.180327868852459</v>
+      </c>
+      <c r="U98" s="12">
         <f t="shared" si="22"/>
-        <v>19.180327868852459</v>
-      </c>
-      <c r="U98" s="12">
-        <f t="shared" si="21"/>
         <v>15.081967213114755</v>
       </c>
       <c r="V98" s="12">
@@ -16316,10 +16599,13 @@
       </c>
       <c r="AF98" s="12"/>
       <c r="AG98" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>40</v>
       </c>
-      <c r="AH98" s="12"/>
+      <c r="AH98" s="12">
+        <f t="shared" si="25"/>
+        <v>9.76</v>
+      </c>
       <c r="AI98" s="12"/>
       <c r="AJ98" s="12"/>
       <c r="AK98" s="12"/>
@@ -16366,7 +16652,7 @@
         <v>32</v>
       </c>
       <c r="L99" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-21</v>
       </c>
       <c r="M99" s="13"/>
@@ -16375,61 +16661,64 @@
         <v>0</v>
       </c>
       <c r="P99" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Q99" s="15"/>
       <c r="R99" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S99" s="25"/>
+      <c r="T99" s="12">
+        <f t="shared" si="23"/>
+        <v>35</v>
+      </c>
+      <c r="U99" s="13">
+        <f t="shared" si="22"/>
+        <v>35</v>
+      </c>
+      <c r="V99" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="W99" s="13">
+        <v>6.6</v>
+      </c>
+      <c r="X99" s="13">
+        <v>18.2</v>
+      </c>
+      <c r="Y99" s="13">
+        <v>7.6</v>
+      </c>
+      <c r="Z99" s="13">
+        <v>12.6</v>
+      </c>
+      <c r="AA99" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="AB99" s="13">
+        <v>14</v>
+      </c>
+      <c r="AC99" s="13">
+        <v>15.6</v>
+      </c>
+      <c r="AD99" s="13">
+        <v>20</v>
+      </c>
+      <c r="AE99" s="13">
+        <v>7</v>
+      </c>
+      <c r="AF99" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="AG99" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S99" s="25"/>
-      <c r="T99" s="12">
-        <f t="shared" si="22"/>
-        <v>35</v>
-      </c>
-      <c r="U99" s="13">
-        <f t="shared" si="21"/>
-        <v>35</v>
-      </c>
-      <c r="V99" s="13">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="W99" s="13">
-        <v>6.6</v>
-      </c>
-      <c r="X99" s="13">
-        <v>18.2</v>
-      </c>
-      <c r="Y99" s="13">
-        <v>7.6</v>
-      </c>
-      <c r="Z99" s="13">
-        <v>12.6</v>
-      </c>
-      <c r="AA99" s="13">
-        <v>21.6</v>
-      </c>
-      <c r="AB99" s="13">
-        <v>14</v>
-      </c>
-      <c r="AC99" s="13">
-        <v>15.6</v>
-      </c>
-      <c r="AD99" s="13">
-        <v>20</v>
-      </c>
-      <c r="AE99" s="13">
-        <v>7</v>
-      </c>
-      <c r="AF99" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG99" s="12">
-        <f t="shared" si="23"/>
+      <c r="AH99" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AH99" s="12"/>
       <c r="AI99" s="12"/>
       <c r="AJ99" s="12"/>
       <c r="AK99" s="12"/>
@@ -16474,68 +16763,71 @@
       <c r="J100" s="12"/>
       <c r="K100" s="12"/>
       <c r="L100" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M100" s="12"/>
       <c r="N100" s="12"/>
       <c r="O100" s="12"/>
       <c r="P100" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q100" s="4"/>
       <c r="R100" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S100" s="25"/>
+      <c r="T100" s="12" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U100" s="12" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V100" s="12">
+        <v>0</v>
+      </c>
+      <c r="W100" s="12">
+        <v>0</v>
+      </c>
+      <c r="X100" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG100" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S100" s="25"/>
-      <c r="T100" s="12" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U100" s="12" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V100" s="12">
+      <c r="AH100" s="12">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="W100" s="12">
-        <v>0</v>
-      </c>
-      <c r="X100" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG100" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH100" s="12"/>
       <c r="AI100" s="12"/>
       <c r="AJ100" s="12"/>
       <c r="AK100" s="12"/>
@@ -16584,7 +16876,7 @@
         <v>174</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-125</v>
       </c>
       <c r="M101" s="12"/>
@@ -16593,7 +16885,7 @@
         <v>200</v>
       </c>
       <c r="P101" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="Q101" s="4">
@@ -16607,11 +16899,11 @@
         <v>400</v>
       </c>
       <c r="T101" s="12">
+        <f t="shared" si="23"/>
+        <v>45.816326530612244</v>
+      </c>
+      <c r="U101" s="12">
         <f t="shared" si="22"/>
-        <v>45.816326530612244</v>
-      </c>
-      <c r="U101" s="12">
-        <f t="shared" si="21"/>
         <v>20.30612244897959</v>
       </c>
       <c r="V101" s="12">
@@ -16648,10 +16940,13 @@
         <v>155</v>
       </c>
       <c r="AG101" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>75</v>
       </c>
-      <c r="AH101" s="12"/>
+      <c r="AH101" s="12">
+        <f t="shared" si="25"/>
+        <v>2.94</v>
+      </c>
       <c r="AI101" s="12"/>
       <c r="AJ101" s="12"/>
       <c r="AK101" s="12"/>
@@ -16704,7 +16999,7 @@
         <v>102</v>
       </c>
       <c r="L102" s="12">
-        <f t="shared" ref="L102:L105" si="30">E102-K102</f>
+        <f t="shared" ref="L102:L105" si="32">E102-K102</f>
         <v>108</v>
       </c>
       <c r="M102" s="12"/>
@@ -16713,24 +17008,24 @@
         <v>216</v>
       </c>
       <c r="P102" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>42</v>
       </c>
       <c r="Q102" s="4">
-        <f t="shared" ref="Q102" si="31">15*P102-O102-F102</f>
+        <f t="shared" ref="Q102" si="33">15*P102-O102-F102</f>
         <v>122</v>
       </c>
       <c r="R102" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>122</v>
       </c>
       <c r="S102" s="25"/>
       <c r="T102" s="12">
+        <f t="shared" si="23"/>
+        <v>15</v>
+      </c>
+      <c r="U102" s="12">
         <f t="shared" si="22"/>
-        <v>15</v>
-      </c>
-      <c r="U102" s="12">
-        <f t="shared" si="21"/>
         <v>12.095238095238095</v>
       </c>
       <c r="V102" s="12">
@@ -16767,10 +17062,13 @@
         <v>156</v>
       </c>
       <c r="AG102" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36.6</v>
       </c>
-      <c r="AH102" s="12"/>
+      <c r="AH102" s="12">
+        <f t="shared" si="25"/>
+        <v>12.6</v>
+      </c>
       <c r="AI102" s="12"/>
       <c r="AJ102" s="12"/>
       <c r="AK102" s="12"/>
@@ -16821,7 +17119,7 @@
         <v>32</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-9</v>
       </c>
       <c r="M103" s="12"/>
@@ -16830,61 +17128,64 @@
         <v>0</v>
       </c>
       <c r="P103" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S103" s="25"/>
+      <c r="T103" s="12">
+        <f t="shared" si="23"/>
+        <v>31.521739130434785</v>
+      </c>
+      <c r="U103" s="12">
+        <f t="shared" si="22"/>
+        <v>31.521739130434785</v>
+      </c>
+      <c r="V103" s="12">
+        <v>0</v>
+      </c>
+      <c r="W103" s="12">
+        <v>0</v>
+      </c>
+      <c r="X103" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="AG103" s="12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S103" s="25"/>
-      <c r="T103" s="12">
-        <f t="shared" si="22"/>
-        <v>31.521739130434785</v>
-      </c>
-      <c r="U103" s="12">
-        <f t="shared" si="21"/>
-        <v>31.521739130434785</v>
-      </c>
-      <c r="V103" s="12">
-        <v>0</v>
-      </c>
-      <c r="W103" s="12">
-        <v>0</v>
-      </c>
-      <c r="X103" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y103" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF103" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG103" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH103" s="12"/>
+      <c r="AH103" s="12">
+        <f t="shared" si="25"/>
+        <v>0.45999999999999996</v>
+      </c>
       <c r="AI103" s="12"/>
       <c r="AJ103" s="12"/>
       <c r="AK103" s="12"/>
@@ -16931,14 +17232,14 @@
         <v>32</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="M104" s="12"/>
       <c r="N104" s="12"/>
       <c r="O104" s="12"/>
       <c r="P104" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6</v>
       </c>
       <c r="Q104" s="4">
@@ -16954,11 +17255,11 @@
         <v>90</v>
       </c>
       <c r="T104" s="12">
+        <f t="shared" si="23"/>
+        <v>14.5</v>
+      </c>
+      <c r="U104" s="12">
         <f t="shared" si="22"/>
-        <v>14.5</v>
-      </c>
-      <c r="U104" s="12">
-        <f t="shared" si="21"/>
         <v>-0.5</v>
       </c>
       <c r="V104" s="12">
@@ -16995,10 +17296,13 @@
         <v>159</v>
       </c>
       <c r="AG104" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
-      <c r="AH104" s="12"/>
+      <c r="AH104" s="12">
+        <f t="shared" si="25"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="AI104" s="12"/>
       <c r="AJ104" s="12"/>
       <c r="AK104" s="12"/>
@@ -17049,7 +17353,7 @@
         <v>69.400000000000006</v>
       </c>
       <c r="L105" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.90500000000000114</v>
       </c>
       <c r="M105" s="12"/>
@@ -17058,7 +17362,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14.061000000000002</v>
       </c>
       <c r="Q105" s="4">
@@ -17066,54 +17370,57 @@
         <v>114.53800000000004</v>
       </c>
       <c r="R105" s="4">
+        <f t="shared" si="26"/>
+        <v>115</v>
+      </c>
+      <c r="S105" s="25"/>
+      <c r="T105" s="12">
+        <f t="shared" si="23"/>
+        <v>13.032856838062726</v>
+      </c>
+      <c r="U105" s="12">
+        <f t="shared" si="22"/>
+        <v>4.8542066709337872</v>
+      </c>
+      <c r="V105" s="12">
+        <v>7.5952000000000002</v>
+      </c>
+      <c r="W105" s="12">
+        <v>13.036799999999999</v>
+      </c>
+      <c r="X105" s="12">
+        <v>2.9236</v>
+      </c>
+      <c r="Y105" s="12">
+        <v>5.2995999999999999</v>
+      </c>
+      <c r="Z105" s="12">
+        <v>4.2118000000000002</v>
+      </c>
+      <c r="AA105" s="12">
+        <v>5.5704000000000002</v>
+      </c>
+      <c r="AB105" s="12">
+        <v>1.3280000000000001</v>
+      </c>
+      <c r="AC105" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="12"/>
+      <c r="AG105" s="12">
         <f t="shared" si="24"/>
         <v>115</v>
       </c>
-      <c r="S105" s="25"/>
-      <c r="T105" s="12">
-        <f t="shared" si="22"/>
-        <v>13.032856838062726</v>
-      </c>
-      <c r="U105" s="12">
-        <f t="shared" si="21"/>
-        <v>4.8542066709337872</v>
-      </c>
-      <c r="V105" s="12">
-        <v>7.5952000000000002</v>
-      </c>
-      <c r="W105" s="12">
-        <v>13.036799999999999</v>
-      </c>
-      <c r="X105" s="12">
-        <v>2.9236</v>
-      </c>
-      <c r="Y105" s="12">
-        <v>5.2995999999999999</v>
-      </c>
-      <c r="Z105" s="12">
-        <v>4.2118000000000002</v>
-      </c>
-      <c r="AA105" s="12">
-        <v>5.5704000000000002</v>
-      </c>
-      <c r="AB105" s="12">
-        <v>1.3280000000000001</v>
-      </c>
-      <c r="AC105" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE105" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF105" s="12"/>
-      <c r="AG105" s="12">
-        <f t="shared" si="23"/>
-        <v>115</v>
-      </c>
-      <c r="AH105" s="12"/>
+      <c r="AH105" s="12">
+        <f t="shared" si="25"/>
+        <v>14.061000000000002</v>
+      </c>
       <c r="AI105" s="12"/>
       <c r="AJ105" s="12"/>
       <c r="AK105" s="12"/>
